--- a/output/2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,6 @@
           <t>+60 3-7847 5990</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Anti-pollution systems, dust collector, blower, spray booth, cyclone. Sede fuori Kedah, copertura Kedah plausibile (operatività dichiarata su tutta la penisola). Email aziendale non reperita con fonte affidabile.</t>
@@ -586,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -628,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -670,7 +669,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -712,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -754,7 +753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +795,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -838,7 +837,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -880,7 +879,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anti-pollution systems, dust collector, blower, spray booth, cyclone. Sede fuori Kedah, copertura Kedah plausibile (operatività dichiarata su tutta la penisola). Email aziendale non reperita con fonte affidabile.</t>
+          <t>Anti-pollution systems, dust collector, blower, spray booth, cyclone. Sede fuori Kedah, copertura Kedah plausibile (operatività dichiarata su tutta la penisola). Email aziendale non reperita con fonte affidabile. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
